--- a/databas.xlsx
+++ b/databas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erik/Documents/StagePatch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCB2F26C-0EDE-474D-9210-740C5B8F92AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D88CCC6-0EE3-CE46-8901-BDFD11B32EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="46">
   <si>
     <t>Instrument</t>
   </si>
@@ -149,6 +149,15 @@
   </si>
   <si>
     <t>DJ</t>
+  </si>
+  <si>
+    <t>TRX</t>
+  </si>
+  <si>
+    <t>TRX ST</t>
+  </si>
+  <si>
+    <t>CLICJ</t>
   </si>
 </sst>
 </file>
@@ -512,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -801,6 +810,39 @@
         <v>3</v>
       </c>
     </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/databas.xlsx
+++ b/databas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erik/Documents/StagePatch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D88CCC6-0EE3-CE46-8901-BDFD11B32EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC982286-CC06-A54D-82C2-98B401CA0D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -157,7 +157,7 @@
     <t>TRX ST</t>
   </si>
   <si>
-    <t>CLICJ</t>
+    <t>CLICK</t>
   </si>
 </sst>
 </file>

--- a/databas.xlsx
+++ b/databas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erik/Documents/StagePatch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC982286-CC06-A54D-82C2-98B401CA0D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9593843A-B82F-FE48-A366-85CE6E425821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="58">
   <si>
     <t>Instrument</t>
   </si>
@@ -88,27 +88,9 @@
     <t>J48</t>
   </si>
   <si>
-    <t>KEY1</t>
-  </si>
-  <si>
     <t>J48 ST</t>
   </si>
   <si>
-    <t>KEY2</t>
-  </si>
-  <si>
-    <t>KEY3</t>
-  </si>
-  <si>
-    <t>KEY4</t>
-  </si>
-  <si>
-    <t>GTR ST 1</t>
-  </si>
-  <si>
-    <t>GTR ST 2</t>
-  </si>
-  <si>
     <t>GTR1</t>
   </si>
   <si>
@@ -154,10 +136,64 @@
     <t>TRX</t>
   </si>
   <si>
-    <t>TRX ST</t>
-  </si>
-  <si>
     <t>CLICK</t>
+  </si>
+  <si>
+    <t>KEY1 L</t>
+  </si>
+  <si>
+    <t>KEY1 R</t>
+  </si>
+  <si>
+    <t>KEY2 L</t>
+  </si>
+  <si>
+    <t>KEY2 R</t>
+  </si>
+  <si>
+    <t>KEY3 L</t>
+  </si>
+  <si>
+    <t>KEY3 R</t>
+  </si>
+  <si>
+    <t>KEY4 L</t>
+  </si>
+  <si>
+    <t>KEY4 R</t>
+  </si>
+  <si>
+    <t>SYNTHBAS</t>
+  </si>
+  <si>
+    <t>GTR ST1 L</t>
+  </si>
+  <si>
+    <t>GTR ST1 R</t>
+  </si>
+  <si>
+    <t>GTR ST2 L</t>
+  </si>
+  <si>
+    <t>GTR ST2 R</t>
+  </si>
+  <si>
+    <t>TRX ST L</t>
+  </si>
+  <si>
+    <t>TRX ST R</t>
+  </si>
+  <si>
+    <t>PERC</t>
+  </si>
+  <si>
+    <t>PERC ST L</t>
+  </si>
+  <si>
+    <t>PERC ST R</t>
+  </si>
+  <si>
+    <t>T3</t>
   </si>
 </sst>
 </file>
@@ -521,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -614,18 +650,18 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
@@ -636,54 +672,54 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
         <v>24</v>
       </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
       <c r="C13" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
         <v>3</v>
@@ -691,10 +727,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
         <v>3</v>
@@ -702,10 +738,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
         <v>3</v>
@@ -713,98 +749,86 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
         <v>3</v>
@@ -812,10 +836,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
         <v>3</v>
@@ -823,10 +847,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
         <v>3</v>
@@ -834,12 +858,141 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" t="s">
         <v>21</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" t="s">
         <v>3</v>
       </c>
     </row>

--- a/databas.xlsx
+++ b/databas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erik/Documents/StagePatch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9593843A-B82F-FE48-A366-85CE6E425821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE1016F-4EB5-5C43-B5A8-D0579588BD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="61">
   <si>
     <t>Instrument</t>
   </si>
@@ -194,6 +194,15 @@
   </si>
   <si>
     <t>T3</t>
+  </si>
+  <si>
+    <t>SAX</t>
+  </si>
+  <si>
+    <t>TRP</t>
+  </si>
+  <si>
+    <t>FIOL</t>
   </si>
 </sst>
 </file>
@@ -250,10 +259,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -557,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -880,10 +892,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" t="s">
-        <v>21</v>
+        <v>58</v>
+      </c>
+      <c r="B31" s="2">
+        <v>4099</v>
       </c>
       <c r="C31" t="s">
         <v>3</v>
@@ -891,10 +903,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" t="s">
-        <v>22</v>
+        <v>59</v>
+      </c>
+      <c r="B32" s="2">
+        <v>4099</v>
       </c>
       <c r="C32" t="s">
         <v>3</v>
@@ -902,7 +914,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>60</v>
+      </c>
+      <c r="B33" s="2">
+        <v>4099</v>
       </c>
       <c r="C33" t="s">
         <v>3</v>
@@ -910,7 +925,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
         <v>21</v>
@@ -921,40 +936,37 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>28</v>
-      </c>
-      <c r="B36" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B38" t="s">
         <v>27</v>
@@ -965,7 +977,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B39" t="s">
         <v>27</v>
@@ -976,23 +988,56 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>31</v>
+      </c>
+      <c r="B42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>36</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B44" t="s">
         <v>35</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C44" t="s">
         <v>3</v>
       </c>
     </row>

--- a/databas.xlsx
+++ b/databas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erik/Documents/StagePatch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE1016F-4EB5-5C43-B5A8-D0579588BD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA8A514-F4CA-774B-8404-5D78750185BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/databas.xlsx
+++ b/databas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erik/Documents/StagePatch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA8A514-F4CA-774B-8404-5D78750185BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06CE729C-B6A0-5140-B130-221B6630AEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="63">
   <si>
     <t>Instrument</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t>FIOL</t>
+  </si>
+  <si>
+    <t>BANJO</t>
+  </si>
+  <si>
+    <t>MANDO</t>
   </si>
 </sst>
 </file>
@@ -569,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -583,42 +589,31 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-    </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -629,29 +624,29 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -662,7 +657,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -673,18 +668,18 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
@@ -695,18 +690,18 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -717,7 +712,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -728,18 +723,18 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
         <v>21</v>
@@ -750,10 +745,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
         <v>3</v>
@@ -761,7 +756,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
       </c>
       <c r="C18" t="s">
         <v>3</v>
@@ -769,10 +767,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
         <v>3</v>
@@ -780,7 +775,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
       </c>
       <c r="C20" t="s">
         <v>3</v>
@@ -788,10 +786,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
         <v>3</v>
@@ -799,7 +794,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
       </c>
       <c r="C22" t="s">
         <v>3</v>
@@ -807,10 +805,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>3</v>
@@ -818,7 +813,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
       </c>
       <c r="C24" t="s">
         <v>3</v>
@@ -826,10 +824,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
         <v>3</v>
@@ -837,7 +832,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
@@ -848,7 +843,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s">
         <v>35</v>
@@ -859,7 +854,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
         <v>35</v>
@@ -870,18 +865,18 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
@@ -892,18 +887,18 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="2">
-        <v>4099</v>
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B32" s="2">
         <v>4099</v>
@@ -914,7 +909,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B33" s="2">
         <v>4099</v>
@@ -925,10 +920,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" t="s">
-        <v>21</v>
+        <v>60</v>
+      </c>
+      <c r="B34" s="2">
+        <v>4099</v>
       </c>
       <c r="C34" t="s">
         <v>3</v>
@@ -936,10 +931,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" t="s">
-        <v>22</v>
+        <v>61</v>
+      </c>
+      <c r="B35" s="2">
+        <v>4099</v>
       </c>
       <c r="C35" t="s">
         <v>3</v>
@@ -947,7 +942,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>53</v>
+        <v>62</v>
+      </c>
+      <c r="B36" s="2">
+        <v>4099</v>
       </c>
       <c r="C36" t="s">
         <v>3</v>
@@ -955,7 +953,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
         <v>21</v>
@@ -966,40 +964,37 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>28</v>
-      </c>
-      <c r="B39" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B41" t="s">
         <v>27</v>
@@ -1010,7 +1005,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B42" t="s">
         <v>27</v>
@@ -1021,23 +1016,56 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>32</v>
+      </c>
+      <c r="B46" t="s">
+        <v>33</v>
+      </c>
+      <c r="C46" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>36</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B47" t="s">
         <v>35</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C47" t="s">
         <v>3</v>
       </c>
     </row>
